--- a/artfynd/A 49778-2025 artfynd.xlsx
+++ b/artfynd/A 49778-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112251522</v>
+        <v>112251523</v>
       </c>
       <c r="B2" t="n">
-        <v>78281</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -777,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112251514</v>
+        <v>112251519</v>
       </c>
       <c r="B3" t="n">
-        <v>96783</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>603662</v>
+        <v>603632</v>
       </c>
       <c r="R3" t="n">
-        <v>6955914</v>
+        <v>6955880</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112251521</v>
+        <v>112251518</v>
       </c>
       <c r="B4" t="n">
-        <v>78752</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>603691</v>
+        <v>603632</v>
       </c>
       <c r="R4" t="n">
-        <v>6955842</v>
+        <v>6955880</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,16 +969,11 @@
         <v>112251524</v>
       </c>
       <c r="B5" t="n">
-        <v>77689</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1083,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112251523</v>
+        <v>112251522</v>
       </c>
       <c r="B6" t="n">
-        <v>77360</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1182,6 +1157,394 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>112251515</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80336</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Långhalshälldalen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>603668</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6955986</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>112251521</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Långhalshälldalen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>603691</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6955842</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>112251520</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Långhalshälldalen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>603632</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6955880</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>112251514</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Långhalshälldalen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>603662</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6955913</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49778-2025 artfynd.xlsx
+++ b/artfynd/A 49778-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112251523</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112251519</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112251518</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112251524</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112251522</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112251515</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112251521</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112251520</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,8 +1590,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112251514</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>